--- a/public/templates/000_pm_suite/01_프로젝트 관리/07_의사소통관리/01_주간보고/프로젝트명_주간업무보고.xlsx
+++ b/public/templates/000_pm_suite/01_프로젝트 관리/07_의사소통관리/01_주간보고/프로젝트명_주간업무보고.xlsx
@@ -318,7 +318,7 @@
  이슈사항</t>
   </si>
   <si>
-    <t>ⓒ Fixframe Inc. All rights reserved.</t>
+    <t>ⓒ Empasy Inc. All rights reserved.</t>
   </si>
   <si>
     <t>단계별 가중치</t>

--- a/public/templates/000_pm_suite/01_프로젝트 관리/07_의사소통관리/01_주간보고/프로젝트명_주간업무보고.xlsx
+++ b/public/templates/000_pm_suite/01_프로젝트 관리/07_의사소통관리/01_주간보고/프로젝트명_주간업무보고.xlsx
@@ -531,7 +531,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-19] SyncGuard AI 주간 업무보고서 (제15주차 — 2026년 08월 2주차) — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-19] SyncFlow AI 주간 업무보고서 (제15주차 — 2026년 08월 2주차) — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>중간 기성 검수(08.19) 시연 및 CR-2026-003 심의</t>
+          <t>중간 기성 검수(08.19) 시연 및 CR-2026-003 검증</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>심의 결과 신호등 리포트 및 대체문구 원클릭 적용 화면 구현</t>
+          <t>검증 결과 신호등 리포트 및 표준수정조항 원클릭 적용 화면 구현</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>HB-SSO 연동 완료 및 ProductLab 02:00 일배치 검증계 테스트 통과</t>
+          <t>HB-SSO 연동 완료 및 PLM-Nexus 02:00 일배치 검증계 테스트 통과</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>MarketingHub 심의 결과 Webhook 콜백 재시도 큐 구현</t>
+          <t>SRM-Portal 검증 결과 Webhook 콜백 재시도 큐 구현</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
